--- a/output/quickfixwick_portfolio_daily.xlsx
+++ b/output/quickfixwick_portfolio_daily.xlsx
@@ -763,7 +763,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="17">

--- a/output/quickfixwick_portfolio_daily.xlsx
+++ b/output/quickfixwick_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$182</f>
+              <f>'equity_curve'!$A$2:$A$184</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$182</f>
+              <f>'equity_curve'!$B$2:$B$184</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>398,510.27</t>
+          <t>414,541.94</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+298.51%</t>
+          <t>+314.54%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>410,829  (+310.83%)</t>
+          <t>427,622  (+327.62%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>5,972  (12.3 pts of return)</t>
+          <t>6,230  (13.1 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>40.0x</t>
+          <t>42.1x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.0%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+3.08R  (best +9.50R)</t>
+          <t>+3.10R  (best +9.50R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,151  (+3.08%)</t>
+          <t>6,321  (+3.10%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-27</t>
+          <t>2025-12-18 -&gt; 2026-07-29</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H182"/>
+  <dimension ref="A1:H184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5410,6 +5410,62 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" s="4" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B183" s="5" t="n">
+        <v>398510.27</v>
+      </c>
+      <c r="C183" s="5" t="n">
+        <v>3985.1</v>
+      </c>
+      <c r="D183" s="5" t="n">
+        <v>394525.17</v>
+      </c>
+      <c r="E183" t="n">
+        <v>1</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures short (risk 3,985)</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" s="4" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B184" s="5" t="n">
+        <v>414541.94</v>
+      </c>
+      <c r="C184" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>414541.94</v>
+      </c>
+      <c r="E184" t="n">
+        <v>0</v>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures long (risk 3,945)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures target_bar (+16,189)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5422,7 +5478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M88"/>
+  <dimension ref="A1:M90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -9944,6 +10000,100 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>2026-07-28</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>1</v>
+      </c>
+      <c r="F89" t="n">
+        <v>4.088</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="H89" t="n">
+        <v>4.062</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>657632.98</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>9141.1</v>
+      </c>
+      <c r="K89" s="6" t="n">
+        <v>37135.71</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>694408.13</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>648491.88</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>9014.040000000001</v>
+      </c>
+      <c r="K90" s="7" t="n">
+        <v>-360.56</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>657272.42</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixwick_portfolio_daily.xlsx
+++ b/output/quickfixwick_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$184</f>
+              <f>'equity_curve'!$A$2:$A$185</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$184</f>
+              <f>'equity_curve'!$B$2:$B$185</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>414,541.94</t>
+          <t>424,799.60</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+314.54%</t>
+          <t>+324.80%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>427,622  (+327.62%)</t>
+          <t>438,359  (+338.36%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6,230  (13.1 pts of return)</t>
+          <t>6,387  (13.6 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>42.1x</t>
+          <t>43.5x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>67.4%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+3.10R  (best +9.50R)</t>
+          <t>+3.09R  (best +9.50R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,321  (+3.10%)</t>
+          <t>6,384  (+3.09%)</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>45% of trading days</t>
+          <t>46% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-29</t>
+          <t>2025-12-18 -&gt; 2026-07-30</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H184"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5443,26 +5443,54 @@
         <v>46232</v>
       </c>
       <c r="B184" s="5" t="n">
-        <v>414541.94</v>
+        <v>414699.75</v>
       </c>
       <c r="C184" s="5" t="n">
+        <v>3945.25</v>
+      </c>
+      <c r="D184" s="5" t="n">
+        <v>410754.5</v>
+      </c>
+      <c r="E184" t="n">
+        <v>1</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures long (risk 3,945)</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>US_Dollar_Index_Futures target_bar (+16,189)</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="4" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B185" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="C185" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="D184" s="5" t="n">
-        <v>414541.94</v>
-      </c>
-      <c r="E184" t="n">
-        <v>0</v>
-      </c>
-      <c r="F184" t="inlineStr"/>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>NY_Natural_Gas_Futures long (risk 3,945)</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>NY_Natural_Gas_Futures open_at_end (open-&gt;closed 0); US_Dollar_Index_Futures target_bar (+16,189)</t>
+      <c r="D185" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="E185" t="n">
+        <v>0</v>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>NY_Natural_Gas_Futures target_bar (+10,100)</t>
         </is>
       </c>
     </row>
@@ -10043,7 +10071,7 @@
         <v>37135.71</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>694408.13</v>
+        <v>694768.6899999999</v>
       </c>
       <c r="M89" t="inlineStr">
         <is>
@@ -10067,14 +10095,22 @@
           <t>2026-07-29</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>1</v>
+      </c>
       <c r="F90" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="G90" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="H90" t="n">
-        <v>-0.04</v>
+        <v>2.56</v>
       </c>
       <c r="I90" s="5" t="n">
         <v>648491.88</v>
@@ -10082,15 +10118,15 @@
       <c r="J90" s="5" t="n">
         <v>9014.040000000001</v>
       </c>
-      <c r="K90" s="7" t="n">
-        <v>-360.56</v>
+      <c r="K90" s="6" t="n">
+        <v>23075.94</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>657272.42</v>
+        <v>717844.63</v>
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>open_at_end</t>
+          <t>target_bar</t>
         </is>
       </c>
     </row>

--- a/output/quickfixwick_portfolio_daily.xlsx
+++ b/output/quickfixwick_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$185</f>
+              <f>'equity_curve'!$A$2:$A$186</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$185</f>
+              <f>'equity_curve'!$B$2:$B$186</f>
             </numRef>
           </val>
         </ser>
@@ -828,7 +828,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>46% of trading days</t>
+          <t>45% of trading days</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-30</t>
+          <t>2025-12-18 -&gt; 2026-07-31</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H185"/>
+  <dimension ref="A1:H186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5493,6 +5493,26 @@
           <t>NY_Natural_Gas_Futures target_bar (+10,100)</t>
         </is>
       </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="4" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B186" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="C186" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D186" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="E186" t="n">
+        <v>0</v>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixwick_portfolio_daily.xlsx
+++ b/output/quickfixwick_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$186</f>
+              <f>'equity_curve'!$A$2:$A$188</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$186</f>
+              <f>'equity_curve'!$B$2:$B$188</f>
             </numRef>
           </val>
         </ser>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-07-31</t>
+          <t>2025-12-18 -&gt; 2026-08-04</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H186"/>
+  <dimension ref="A1:H188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5513,6 +5513,46 @@
       <c r="F186" t="inlineStr"/>
       <c r="G186" t="inlineStr"/>
       <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" s="4" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B187" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="C187" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D187" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="E187" t="n">
+        <v>0</v>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" s="4" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B188" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="C188" s="5" t="n">
+        <v>-0</v>
+      </c>
+      <c r="D188" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="E188" t="n">
+        <v>0</v>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/quickfixwick_portfolio_daily.xlsx
+++ b/output/quickfixwick_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$188</f>
+              <f>'equity_curve'!$A$2:$A$190</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$188</f>
+              <f>'equity_curve'!$B$2:$B$190</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>424,799.60</t>
+          <t>435,579.68</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+324.80%</t>
+          <t>+335.58%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>438,359  (+338.36%)</t>
+          <t>449,508  (+349.51%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6,387  (13.6 pts of return)</t>
+          <t>6,411  (13.9 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>43.5x</t>
+          <t>44.9x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>68.1%</t>
         </is>
       </c>
     </row>
@@ -742,7 +742,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>+3.09R  (best +9.50R)</t>
+          <t>+3.03R  (best +9.50R)</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>6,384  (+3.09%)</t>
+          <t>6,353  (+3.03%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-04</t>
+          <t>2025-12-18 -&gt; 2026-08-06</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5554,6 +5554,62 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr"/>
     </row>
+    <row r="189">
+      <c r="A189" s="4" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B189" s="5" t="n">
+        <v>424799.6</v>
+      </c>
+      <c r="C189" s="5" t="n">
+        <v>12616.97</v>
+      </c>
+      <c r="D189" s="5" t="n">
+        <v>412182.63</v>
+      </c>
+      <c r="E189" t="n">
+        <v>3</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures, Nasdaq_100_E_mini, S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures short (risk 4,248); Nasdaq_100_E_mini short (risk 4,206); S_P_500_E_mini short (risk 4,163)</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" s="4" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B190" s="5" t="n">
+        <v>435579.68</v>
+      </c>
+      <c r="C190" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D190" s="5" t="n">
+        <v>435579.68</v>
+      </c>
+      <c r="E190" t="n">
+        <v>0</v>
+      </c>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX short (risk 4,122)</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini target_bar (+8,402); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini target_bar (+2,400)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -5566,7 +5622,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M90"/>
+  <dimension ref="A1:M94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -10190,6 +10246,194 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NY_Platinum_Futures</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>717844.63</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>9978.040000000001</v>
+      </c>
+      <c r="K91" s="7" t="n">
+        <v>-34.65</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>737451.55</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Nasdaq_100_E_mini</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>1</v>
+      </c>
+      <c r="F92" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>1.998</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>707866.59</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>9839.35</v>
+      </c>
+      <c r="K92" s="6" t="n">
+        <v>19657.93</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>737486.2</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>S_P_500_E_mini</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>1</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>698027.24</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>9702.58</v>
+      </c>
+      <c r="K93" s="6" t="n">
+        <v>5592.34</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>743043.89</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>target_bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-0.002</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>688324.66</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>9567.709999999999</v>
+      </c>
+      <c r="K94" s="7" t="n">
+        <v>-16.36</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>717828.27</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/quickfixwick_portfolio_daily.xlsx
+++ b/output/quickfixwick_portfolio_daily.xlsx
@@ -203,12 +203,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'equity_curve'!$A$2:$A$190</f>
+              <f>'equity_curve'!$A$2:$A$191</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'equity_curve'!$B$2:$B$190</f>
+              <f>'equity_curve'!$B$2:$B$191</f>
             </numRef>
           </val>
         </ser>
@@ -636,7 +636,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>435,579.68</t>
+          <t>431,408.58</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>+335.58%</t>
+          <t>+331.41%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>449,508  (+349.51%)</t>
+          <t>445,255  (+345.25%)</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>6,411  (13.9 pts of return)</t>
+          <t>6,461  (13.8 pts of return)</t>
         </is>
       </c>
     </row>
@@ -696,7 +696,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>44.9x</t>
+          <t>44.4x</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12">
@@ -718,7 +718,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.4%</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>-2,009  (-1.13%)</t>
+          <t>-2,080  (-1.13%)</t>
         </is>
       </c>
     </row>
@@ -852,7 +852,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2025-12-18 -&gt; 2026-08-06</t>
+          <t>2025-12-18 -&gt; 2026-08-07</t>
         </is>
       </c>
     </row>
@@ -891,7 +891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H190"/>
+  <dimension ref="A1:H191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5587,18 +5587,22 @@
         <v>46240</v>
       </c>
       <c r="B190" s="5" t="n">
-        <v>435579.68</v>
+        <v>435601.48</v>
       </c>
       <c r="C190" s="5" t="n">
-        <v>0</v>
+        <v>8369.82</v>
       </c>
       <c r="D190" s="5" t="n">
-        <v>435579.68</v>
+        <v>427231.65</v>
       </c>
       <c r="E190" t="n">
-        <v>0</v>
-      </c>
-      <c r="F190" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX, NY_Platinum_Futures</t>
+        </is>
+      </c>
       <c r="G190" t="inlineStr">
         <is>
           <t>Gold_Futures_COMEX short (risk 4,122)</t>
@@ -5606,7 +5610,35 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Gold_Futures_COMEX open_at_end (open-&gt;closed 0); Nasdaq_100_E_mini target_bar (+8,402); NY_Platinum_Futures open_at_end (open-&gt;closed 0); S_P_500_E_mini target_bar (+2,400)</t>
+          <t>Nasdaq_100_E_mini target_bar (+8,402); S_P_500_E_mini target_bar (+2,400)</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="4" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B191" s="5" t="n">
+        <v>431408.58</v>
+      </c>
+      <c r="C191" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D191" s="5" t="n">
+        <v>431408.58</v>
+      </c>
+      <c r="E191" t="n">
+        <v>0</v>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures short (risk 4,272); NY_Palladium_Futures short (risk 4,230)</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Gold_Futures_COMEX stop (-4,150); NY_Copper_Futures open_at_end (open-&gt;closed 0); NY_Palladium_Futures open_at_end (open-&gt;closed 0); NY_Platinum_Futures open_at_end (open-&gt;closed 0)</t>
         </is>
       </c>
     </row>
@@ -5622,7 +5654,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M94"/>
+  <dimension ref="A1:M96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -5634,7 +5666,7 @@
     <col width="8" customWidth="1" min="7" max="7"/>
     <col width="8" customWidth="1" min="8" max="8"/>
     <col width="15" customWidth="1" min="9" max="9"/>
-    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="15" customWidth="1" min="12" max="12"/>
     <col width="13" customWidth="1" min="13" max="13"/>
@@ -10281,7 +10313,7 @@
         <v>-34.65</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>737451.55</v>
+        <v>733361.04</v>
       </c>
       <c r="M91" t="inlineStr">
         <is>
@@ -10332,7 +10364,7 @@
         <v>19657.93</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>737486.2</v>
+        <v>737502.55</v>
       </c>
       <c r="M92" t="inlineStr">
         <is>
@@ -10383,7 +10415,7 @@
         <v>5592.34</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>743043.89</v>
+        <v>743094.89</v>
       </c>
       <c r="M93" t="inlineStr">
         <is>
@@ -10407,14 +10439,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>1</v>
+      </c>
       <c r="F94" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="G94" t="n">
-        <v>0.002</v>
+        <v>0.007</v>
       </c>
       <c r="H94" t="n">
-        <v>-0.002</v>
+        <v>-1.007</v>
       </c>
       <c r="I94" s="5" t="n">
         <v>688324.66</v>
@@ -10423,12 +10463,98 @@
         <v>9567.709999999999</v>
       </c>
       <c r="K94" s="7" t="n">
-        <v>-16.36</v>
+        <v>-9633.129999999999</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>717828.27</v>
+        <v>733461.76</v>
       </c>
       <c r="M94" t="inlineStr">
+        <is>
+          <t>stop</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>NY_Copper_Futures</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.003</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-0.003</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>723549.14</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>10057.33</v>
+      </c>
+      <c r="K95" s="7" t="n">
+        <v>-27.18</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>733434.58</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>open_at_end</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>NY_Palladium_Futures</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>short</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>0</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-0.004</v>
+      </c>
+      <c r="I96" s="5" t="n">
+        <v>713491.8100000001</v>
+      </c>
+      <c r="J96" s="5" t="n">
+        <v>9917.540000000001</v>
+      </c>
+      <c r="K96" s="7" t="n">
+        <v>-38.89</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>733395.6899999999</v>
+      </c>
+      <c r="M96" t="inlineStr">
         <is>
           <t>open_at_end</t>
         </is>
